--- a/outputs/E_vertical_nested_lines.xlsx
+++ b/outputs/E_vertical_nested_lines.xlsx
@@ -10,25 +10,27 @@
     <sheet name="Data 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Validation Report" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Page Audit" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Provenance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Read me" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Cell Evidence" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Verification" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Constraints" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Repair Proposals" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Correction History" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Join Receipt" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Read me" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cell Evidence" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Verification" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Constraints" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Repair Proposals" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Correction History" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data 1'!$A$1:$J$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Validation Report'!$A$1:$H$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Page Audit'!$A$1:$L$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Provenance'!$A$1:$E$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Read me'!$A$1:$B$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Cell Evidence'!$A$1:$M$91</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Verification'!$A$1:$B$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Constraints'!$A$1:$H$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Correction History'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Join Receipt'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Provenance'!$A$1:$E$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Read me'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Cell Evidence'!$A$1:$O$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Verification'!$A$1:$B$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Constraints'!$A$1:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Repair Proposals'!$A$1:$I$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Correction History'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1000,6 +1002,79 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Excel row</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Observed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Supporting equations</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Caution</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
@@ -1259,7 +1334,7 @@
         <v>0.98</v>
       </c>
       <c r="E2" s="6" t="n">
-        <v>0.06</v>
+        <v>0.303</v>
       </c>
       <c r="F2" s="6" t="inlineStr">
         <is>
@@ -1290,6 +1365,103 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Data sheet</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Source pages</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Page joins</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Repeated headers removed</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Split rows recovered</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PDF page</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Source rows on page</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Output rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Data 1</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:H2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1506,7 +1678,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1550,7 +1722,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.106</v>
+        <v>1.068</v>
       </c>
     </row>
     <row r="4" ht="119" customHeight="1">
@@ -1679,13 +1851,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1701,6 +1873,8 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="17" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="65" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1769,6 +1943,16 @@
           <t>Role</t>
         </is>
       </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Location status</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Location reason</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="6" t="inlineStr">
@@ -1814,6 +1998,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N2" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -1859,6 +2053,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
@@ -1904,6 +2108,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N4" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
@@ -1949,6 +2163,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
@@ -1994,6 +2218,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N6" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -2039,6 +2273,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
@@ -2084,6 +2328,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
@@ -2129,6 +2383,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
@@ -2174,6 +2438,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
@@ -2219,6 +2493,16 @@
           <t>header</t>
         </is>
       </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -2264,6 +2548,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="17" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
@@ -2309,6 +2603,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O13" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="17" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -2354,6 +2658,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
@@ -2399,6 +2713,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="17" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
@@ -2444,6 +2768,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O16" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="17" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
@@ -2489,6 +2823,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O17" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="17" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
@@ -2534,6 +2878,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="17" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -2579,6 +2933,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="17" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
@@ -2624,6 +2988,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O20" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="17" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
@@ -2669,6 +3043,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="17" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
@@ -2714,6 +3098,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="17" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
@@ -2759,6 +3153,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="17" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
@@ -2804,6 +3208,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O24" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="17" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -2849,6 +3263,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="17" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
@@ -2894,6 +3318,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="17" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
@@ -2939,6 +3373,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="17" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
@@ -2984,6 +3428,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O28" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="17" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
@@ -3029,6 +3483,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="17" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
@@ -3074,6 +3538,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="17" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
@@ -3119,6 +3593,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="17" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
@@ -3164,6 +3648,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="17" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
@@ -3209,6 +3703,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="17" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
@@ -3254,6 +3758,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="17" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -3299,6 +3813,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="17" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
@@ -3344,6 +3868,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="17" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -3389,6 +3923,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="17" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
@@ -3434,6 +3978,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="17" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
@@ -3479,6 +4033,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="17" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
@@ -3524,6 +4088,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N40" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="17" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
@@ -3569,6 +4143,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N41" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="17" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
@@ -3614,6 +4198,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N42" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="17" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
@@ -3659,6 +4253,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N43" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O43" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="17" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -3704,6 +4308,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N44" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="17" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
@@ -3749,6 +4363,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N45" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="17" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
@@ -3794,6 +4418,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N46" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="17" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
@@ -3839,6 +4473,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N47" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O47" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="17" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
@@ -3884,6 +4528,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N48" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="17" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
@@ -3929,6 +4583,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="17" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
@@ -3974,6 +4638,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="17" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
@@ -4019,6 +4693,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="17" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
@@ -4064,6 +4748,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="17" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
@@ -4109,6 +4803,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="17" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
@@ -4154,6 +4858,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="17" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
@@ -4199,6 +4913,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="17" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
@@ -4244,6 +4968,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N56" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O56" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="17" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
@@ -4289,6 +5023,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N57" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O57" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="17" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
@@ -4334,6 +5078,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N58" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O58" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="17" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
@@ -4379,6 +5133,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N59" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O59" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="17" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
@@ -4424,6 +5188,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N60" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O60" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="17" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
@@ -4469,6 +5243,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O61" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="17" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
@@ -4514,6 +5298,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O62" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="17" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
@@ -4559,6 +5353,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="17" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
@@ -4604,6 +5408,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="17" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
@@ -4649,6 +5463,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O65" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="17" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
@@ -4694,6 +5518,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N66" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O66" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="17" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
@@ -4739,6 +5573,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O67" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="17" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
@@ -4784,6 +5628,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="17" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
@@ -4829,6 +5683,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O69" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="17" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
@@ -4874,6 +5738,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O70" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="17" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
@@ -4919,6 +5793,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O71" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="17" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
@@ -4964,6 +5848,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O72" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="17" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
@@ -5009,6 +5903,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O73" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="17" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
@@ -5054,6 +5958,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="17" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
@@ -5099,6 +6013,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O75" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="17" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
@@ -5144,6 +6068,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O76" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="17" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
@@ -5189,6 +6123,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="17" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
@@ -5234,6 +6178,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="17" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
@@ -5279,6 +6233,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="17" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
@@ -5324,6 +6288,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="17" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
@@ -5369,6 +6343,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O81" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="17" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
@@ -5414,6 +6398,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O82" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="17" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
@@ -5459,6 +6453,16 @@
           <t>vertical_merge_expansion</t>
         </is>
       </c>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O83" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="17" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
@@ -5504,6 +6508,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O84" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="17" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
@@ -5549,6 +6563,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="17" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -5594,6 +6618,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="17" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
@@ -5639,6 +6673,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="17" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
@@ -5684,6 +6728,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N88" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="17" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
@@ -5729,6 +6783,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N89" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="17" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
@@ -5774,6 +6838,16 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N90" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="17" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
@@ -5819,23 +6893,33 @@
           <t>extracted</t>
         </is>
       </c>
+      <c r="N91" s="6" t="inlineStr">
+        <is>
+          <t>located</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr">
+        <is>
+          <t>At least one original reading has an exact source bounding box.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M91"/>
+  <autoFilter ref="A1:O91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
     <col width="65" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -5871,7 +6955,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>ab02e1bb3b3915a9c2203788b7b3cd117352f26a54e01b12359fd131761d2b1b</t>
+          <t>202bdc4988e6a649d87b3d4b0fb3432c6f7b7ec70a306b841c24970db4502584</t>
         </is>
       </c>
     </row>
@@ -5910,70 +6994,122 @@
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>cells</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>80</v>
+          <t>Export type</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Draft Excel</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>cells with source boxes</t>
+          <t>Non-empty exported cells</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>equations</t>
+          <t>Cells with source boxes</t>
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>equation checks</t>
+          <t>Cells requiring full-page evidence review</t>
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>failed equation checks</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>0</v>
+          <t>Cell source-box coverage</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
+          <t>cells</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>cells with source boxes</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>equations</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>equation checks</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>failed equation checks</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
           <t>proposals with multiple equations</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B17" s="6" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B12"/>
+  <autoFilter ref="A1:B17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6070,77 +7206,4 @@
   <autoFilter ref="A1:H2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Table</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Excel row</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Observed</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Supporting equations</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Caution</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>